--- a/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico.xlsx
+++ b/Hardware/Analisis Eléctrico y Térmico/Analisiselectrico.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
   <si>
     <t>TOTAL</t>
   </si>
@@ -78,13 +78,198 @@
   </si>
   <si>
     <t>LIPO BAT</t>
+  </si>
+  <si>
+    <t>Currents (µA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charging </t>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 0 mA, V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Note 1  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">           V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OUT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 0.8V to 5.0V </t>
+    </r>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>Does not include current through the pull-up resistor on USBDP In USB suspend mode, the D+ voltage can go up to a maximum of 3.8 V.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> VIN ≥ 2.3V,  VIN ≥ VOUT(MAX) + VDROPOUT(MAX), VIN ≥ 2.3V,  VIN ≥ VOUT(MAX) + VDROPOUT(MAX)    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>USB 2.0 FS, UART at 1-Mbps single channel, no GPIO switching at V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= 5 V, V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CCIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 5 V</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">per supply pin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 000 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +280,28 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,9 +328,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,15 +635,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" customWidth="1"/>
     <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" customWidth="1"/>
@@ -454,12 +686,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="1"/>
+      <c r="G3" s="5"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
         <v>2</v>
@@ -484,39 +717,107 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D8" s="1" t="s">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1500</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="6" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D13" s="1" t="s">
+      <c r="B6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D7" s="1" t="s">
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:14" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="D14" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D17" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
